--- a/salon_forms/006_hair_color_consultation_form--salon_forms.xlsx
+++ b/salon_forms/006_hair_color_consultation_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select Face Shape</t>
+          <t>Face Shape 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select Skin Tone</t>
+          <t>Skin Tone 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select Your Desired Hair Hue</t>
+          <t>Hair Hue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select Hair Length</t>
+          <t>Hair Length 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Select Hair Condition</t>
+          <t>Hair Condition 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1500,34 +1500,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_condition_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>hair_condition_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>thick</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thick</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dry</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>oily</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oily</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>damaged</t>
+          <t>wiry</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Damaged</t>
+          <t>Wiry</t>
         </is>
       </c>
     </row>
@@ -1607,63 +1607,63 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>curled</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Curled</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hair_condition_choices</t>
+          <t>hair_texture_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>curly</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Curly</t>
+          <t>Fine</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hair_condition_choices</t>
+          <t>hair_texture_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wiry</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wiry</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hair_condition_choices</t>
+          <t>hair_texture_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>curled</t>
+          <t>coarse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Curled</t>
+          <t>Coarse</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fine</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1692,87 +1692,87 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>hair_density_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>coarse</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Fine</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>hair_density_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>hair_density_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>coarse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Coarse</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>hair_density_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>hair_density_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,279 +1789,279 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hair_texture_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fine</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fine</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>coarse</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>face_shape_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>triangular</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Triangular</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>tan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Tan</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hair_density_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fine</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>skin_tone_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>triangular</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Triangular</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>triangular</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Triangular</t>
+          <t>Deep</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>hair_hue_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>face_shape_choices</t>
+          <t>face_shape_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,126 +2078,126 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>face_shape_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>face_shape_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>face_shape_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>tan</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>face_shape_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>triangular</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Triangular</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>skin_tone_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>skin_tone_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>skin_tone_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>tan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Tan</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>skin_tone_choices</t>
+          <t>skin_tone_2_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,109 +2214,109 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>skin_tone_2_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>natural</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Warm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>cool</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Cool</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Deep</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Deep</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>hair_hue_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,933 +2333,389 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>hair_hue_choices</t>
+          <t>stylist_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>stylist_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>sally</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Sally</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>stylist_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>stylist_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>stylist_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>doe</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Doe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>triangular</t>
+          <t>consultation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Triangular</t>
+          <t>Consultation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>triangular</t>
+          <t>cut</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Triangular</t>
+          <t>Cut</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>face_shape_2_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>trim</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Trim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>services_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>style</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Style</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>tan</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>pixie</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Pixie</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_length_2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>bobbed</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Bobbed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>skin_tone_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>natural</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Warm</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>wiry</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Deep</t>
+          <t>Wiry</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>hair_hue_2_choices</t>
+          <t>hair_condition_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cool</t>
+          <t>curled</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
-        <is>
-          <t>Cool</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>hair_hue_2_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Very</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>hair_hue_2_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>jimmy</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Jimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>sally</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Sally</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>jane</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>john</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>doe</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>doe</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>jane</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>stylist_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>john</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Consultation</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>cut</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>style</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Trim</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>style</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Style</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>services_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Consultation</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>pixie</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Pixie</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>bob</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>hair_length_2_choices</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>bobbed</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Bobbed</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>dry</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Dry</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>oily</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Oily</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>damaged</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Damaged</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>curly</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Curly</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>wiry</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Wiry</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>hair_condition_2_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>curled</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
         <is>
           <t>Curled</t>
         </is>
